--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_4_R1.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_4_R1.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2999</v>
+        <v>6.6269</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3965</v>
+        <v>6.5891</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.09669999999999999</v>
+        <v>0.0378</v>
       </c>
       <c r="G2" t="n">
         <v>6.3988</v>
@@ -610,13 +610,13 @@
         <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9366</v>
+        <v>-0.6095</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0351</v>
+        <v>0.1575</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9014</v>
+        <v>-0.767</v>
       </c>
       <c r="V2" t="n">
         <v>0.1418</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.4117</v>
+        <v>4.3412</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4566</v>
+        <v>3.5876</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9552</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>3.7322</v>
@@ -688,13 +688,13 @@
         <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2336</v>
+        <v>0.163</v>
       </c>
       <c r="T3" t="n">
-        <v>1.274</v>
+        <v>0.405</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0404</v>
+        <v>-0.242</v>
       </c>
       <c r="V3" t="n">
         <v>0.6778999999999999</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4721</v>
+        <v>3.4692</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8791</v>
+        <v>3.6746</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.407</v>
+        <v>-0.2054</v>
       </c>
       <c r="G4" t="n">
         <v>2.9613</v>
@@ -766,13 +766,13 @@
         <v>2.5515</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7934</v>
+        <v>-0.7962</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3778</v>
+        <v>0.1733</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.1712</v>
+        <v>-0.9695</v>
       </c>
       <c r="V4" t="n">
         <v>1.0722</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. PETRUSEV</t>
+          <t>D. BACON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,31 +799,31 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1235</v>
+        <v>2.08</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1175</v>
+        <v>2.3165</v>
       </c>
       <c r="F5" t="n">
-        <v>2.241</v>
+        <v>-0.2365</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7799</v>
+        <v>2.9321</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4721</v>
+        <v>0.677</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3078</v>
+        <v>2.2552</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2792</v>
+        <v>3.4328</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5</v>
+        <v>0.6491</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2208</v>
+        <v>2.7837</v>
       </c>
       <c r="M5" t="n">
         <v>-0.5007</v>
@@ -835,37 +835,37 @@
         <v>-0.5286</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3195</v>
+        <v>1.8556</v>
       </c>
       <c r="S5" t="n">
-        <v>1.7436</v>
+        <v>-0.4758</v>
       </c>
       <c r="T5" t="n">
-        <v>1.3214</v>
+        <v>0.0435</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4222</v>
+        <v>-0.5192</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. BACON</t>
+          <t>J. ANDERSON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3723</v>
+        <v>1.896</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6088</v>
+        <v>0.2811</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2365</v>
+        <v>1.6149</v>
       </c>
       <c r="G6" t="n">
-        <v>2.9321</v>
+        <v>0.7609</v>
       </c>
       <c r="H6" t="n">
-        <v>0.677</v>
+        <v>1.3866</v>
       </c>
       <c r="I6" t="n">
-        <v>2.2552</v>
+        <v>-0.6257</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4328</v>
+        <v>0.45</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6491</v>
+        <v>1.1259</v>
       </c>
       <c r="L6" t="n">
-        <v>2.7837</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5007</v>
+        <v>0.3109</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0279</v>
+        <v>0.2606</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5286</v>
+        <v>0.0502</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1835</v>
+        <v>-0.2566</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6642</v>
+        <v>-0.1689</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5192</v>
+        <v>-0.0876</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. ANDERSON</t>
+          <t>M. WRIGHT IV</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.292</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2221</v>
+        <v>0.6045</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5141</v>
+        <v>0.274</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7609</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3866</v>
+        <v>-2.3733</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6257</v>
+        <v>2.282</v>
       </c>
       <c r="J7" t="n">
-        <v>0.45</v>
+        <v>0.3093</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1259</v>
+        <v>-2.8191</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6758999999999999</v>
+        <v>3.1284</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3109</v>
+        <v>-0.4006</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2606</v>
+        <v>0.4458</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0502</v>
+        <v>-0.8464</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3917</v>
+        <v>3.0154</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3917</v>
+        <v>3.0154</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8606</v>
+        <v>-0.8316</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6721</v>
+        <v>0.2952</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1885</v>
+        <v>-1.1268</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. KONDIC</t>
+          <t>F. PETRUSEV</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3589</v>
+        <v>0.8250999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4395</v>
+        <v>-0.9118000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0806</v>
+        <v>1.7369</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7246</v>
+        <v>-0.7799</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1357</v>
+        <v>-0.4721</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5889</v>
+        <v>-0.3078</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5889</v>
+        <v>-0.2792</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5889</v>
+        <v>0.2208</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1357</v>
+        <v>-0.5007</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1357</v>
+        <v>0.0279</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-0.5286</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.1598</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.3195</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.08210000000000001</v>
+        <v>0.4452</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1494</v>
+        <v>0.5272</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0672</v>
+        <v>-0.0819</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. DANGUBIC</t>
+          <t>K. KONDIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1354</v>
+        <v>0.4597</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0411</v>
+        <v>0.4395</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1765</v>
+        <v>0.0202</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1801</v>
+        <v>0.7246</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1801</v>
+        <v>0.1357</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.5889</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0336</v>
+        <v>0.5889</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0336</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.5889</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1465</v>
+        <v>0.1357</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1465</v>
+        <v>0.1357</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1349</v>
+        <v>0.0187</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0747</v>
+        <v>-0.1494</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0602</v>
+        <v>0.168</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1418</v>
+        <v>-0.2836</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1418</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. WRIGHT IV</t>
+          <t>N. DANGUBIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0557</v>
+        <v>0.4049</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0167</v>
+        <v>0.1948</v>
       </c>
       <c r="F10" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.2101</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.09130000000000001</v>
+        <v>0.1801</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.3733</v>
+        <v>0.1801</v>
       </c>
       <c r="I10" t="n">
-        <v>2.282</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3093</v>
+        <v>0.0336</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.8191</v>
+        <v>0.0336</v>
       </c>
       <c r="L10" t="n">
-        <v>3.1284</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4006</v>
+        <v>0.1465</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4458</v>
+        <v>0.1465</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8464</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3.0154</v>
+        <v>0.232</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3.0154</v>
+        <v>0.232</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6544</v>
+        <v>0.1346</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.326</v>
+        <v>0.1612</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.3284</v>
+        <v>-0.0266</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.214</v>
+        <v>-0.1418</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.214</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1872</v>
+        <v>-0.002</v>
       </c>
       <c r="E11" t="n">
-        <v>0.334</v>
+        <v>0.4519</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5211</v>
+        <v>-0.4539</v>
       </c>
       <c r="G11" t="n">
         <v>-0.1573</v>
@@ -1312,13 +1312,13 @@
         <v>0.4639</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4938</v>
+        <v>-0.3086</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1415</v>
+        <v>-0.0235</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3523</v>
+        <v>-0.2851</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3407</v>
+        <v>-0.5759</v>
       </c>
       <c r="E12" t="n">
         <v>-1.2344</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8937</v>
+        <v>0.6585</v>
       </c>
       <c r="G12" t="n">
         <v>0.3038</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5153</v>
+        <v>0.2801</v>
       </c>
       <c r="T12" t="n">
         <v>-0.0747</v>
       </c>
       <c r="U12" t="n">
-        <v>0.59</v>
+        <v>0.3547</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.0308</v>
+        <v>-4.6941</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.2279</v>
+        <v>-3.992</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8028999999999999</v>
+        <v>-0.7020999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-3.098</v>
@@ -1468,13 +1468,13 @@
         <v>0.4639</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1647</v>
+        <v>0.172</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0668</v>
+        <v>0.1691</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.098</v>
+        <v>0.0029</v>
       </c>
       <c r="V13" t="n">
         <v>-1.0722</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>14.9628</v>
+        <v>15.7095</v>
       </c>
       <c r="E14" t="n">
-        <v>11.2548</v>
+        <v>12.0014</v>
       </c>
       <c r="F14" t="n">
-        <v>3.7081</v>
+        <v>3.708</v>
       </c>
       <c r="G14" t="n">
         <v>13.8673</v>
       </c>
       <c r="H14" t="n">
-        <v>4.933899999999999</v>
+        <v>4.9339</v>
       </c>
       <c r="I14" t="n">
         <v>8.9337</v>
@@ -1546,13 +1546,13 @@
         <v>15.0769</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.811500000000001</v>
+        <v>-2.064700000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7686999999999999</v>
+        <v>1.5155</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.5802</v>
+        <v>-3.5801</v>
       </c>
       <c r="V14" t="n">
         <v>-1.8919</v>
@@ -1561,7 +1561,7 @@
         <v>4.5724</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.464300000000001</v>
+        <v>-6.4643</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4183</v>
+        <v>1.2116</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1233</v>
+        <v>1.0618</v>
       </c>
       <c r="F15" t="n">
-        <v>0.295</v>
+        <v>0.1498</v>
       </c>
       <c r="G15" t="n">
         <v>-0.9188</v>
@@ -1624,13 +1624,13 @@
         <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1258</v>
+        <v>0.919</v>
       </c>
       <c r="T15" t="n">
-        <v>2.0998</v>
+        <v>1.0383</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0259</v>
+        <v>-0.1193</v>
       </c>
       <c r="V15" t="n">
         <v>0.2836</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. JONES</t>
+          <t>A. POKUSEVSKI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7616000000000001</v>
+        <v>0.6853</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7579</v>
+        <v>1.3127</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9963</v>
+        <v>-0.6274</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6567</v>
+        <v>2.4573</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1079</v>
+        <v>0.0349</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5488</v>
+        <v>2.4225</v>
       </c>
       <c r="J16" t="n">
-        <v>3.7151</v>
+        <v>2.3859</v>
       </c>
       <c r="K16" t="n">
-        <v>2.4269</v>
+        <v>0.0672</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2882</v>
+        <v>2.3187</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0583</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.319</v>
+        <v>-0.0323</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7393999999999999</v>
+        <v>0.1038</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.7834</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.7112</v>
+        <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="S16" t="n">
-        <v>1.8187</v>
+        <v>0.228</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6122</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2065</v>
+        <v>0.1415</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9304</v>
+        <v>-1.0722</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>-1.0722</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3287</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9913999999999999</v>
+        <v>1.3452</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6626</v>
+        <v>-0.7299</v>
       </c>
       <c r="G17" t="n">
         <v>0.6955</v>
@@ -1780,13 +1780,13 @@
         <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5834</v>
+        <v>-0.2967</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2592</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3242</v>
+        <v>-0.3914</v>
       </c>
       <c r="V17" t="n">
         <v>1.6083</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. POKUSEVSKI</t>
+          <t>V. MARINKOVIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.315</v>
+        <v>0.0585</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0768</v>
+        <v>0.5738</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7618</v>
+        <v>-0.5153</v>
       </c>
       <c r="G18" t="n">
-        <v>2.4573</v>
+        <v>0.0319</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0349</v>
+        <v>-0.9351</v>
       </c>
       <c r="I18" t="n">
-        <v>2.4225</v>
+        <v>0.967</v>
       </c>
       <c r="J18" t="n">
-        <v>2.3859</v>
+        <v>0.4754</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0672</v>
+        <v>-0.7023</v>
       </c>
       <c r="L18" t="n">
-        <v>2.3187</v>
+        <v>1.1778</v>
       </c>
       <c r="M18" t="n">
-        <v>0.07140000000000001</v>
+        <v>-0.4435</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0323</v>
+        <v>-0.2327</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1038</v>
+        <v>-0.2108</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0.232</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1423</v>
+        <v>-0.2054</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1494</v>
+        <v>0.0984</v>
       </c>
       <c r="U18" t="n">
-        <v>0.007</v>
+        <v>-0.3038</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. OSETKOWSKI</t>
+          <t>T. JONES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2267</v>
+        <v>0.026</v>
       </c>
       <c r="E19" t="n">
-        <v>2.8159</v>
+        <v>0.9322</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.5892</v>
+        <v>-0.9062</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.0522</v>
+        <v>2.6567</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5498</v>
+        <v>2.1079</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.5023</v>
+        <v>0.5488</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0721</v>
+        <v>3.7151</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4636</v>
+        <v>2.4269</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3914</v>
+        <v>1.2882</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.98</v>
+        <v>-1.0583</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0862</v>
+        <v>-0.319</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.8938</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6959</v>
+        <v>-2.7834</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.232</v>
+        <v>-3.7112</v>
       </c>
       <c r="R19" t="n">
         <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>0.369</v>
+        <v>1.0831</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8338</v>
+        <v>0.7866</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4648</v>
+        <v>0.2965</v>
       </c>
       <c r="V19" t="n">
-        <v>1.214</v>
+        <v>-0.9304</v>
       </c>
       <c r="W19" t="n">
-        <v>2.2862</v>
+        <v>0.1418</v>
       </c>
       <c r="X19" t="n">
         <v>-1.0722</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V. MARINKOVIC</t>
+          <t>D. OSETKOWSKI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5141</v>
+        <v>-0.1107</v>
       </c>
       <c r="E20" t="n">
-        <v>0.102</v>
+        <v>2.3441</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6162</v>
+        <v>-2.4548</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0319</v>
+        <v>-2.0522</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9351</v>
+        <v>-0.5498</v>
       </c>
       <c r="I20" t="n">
-        <v>0.967</v>
+        <v>-1.5023</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4754</v>
+        <v>-0.0721</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7023</v>
+        <v>-0.4636</v>
       </c>
       <c r="L20" t="n">
-        <v>1.1778</v>
+        <v>0.3914</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4435</v>
+        <v>-1.98</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2327</v>
+        <v>-0.0862</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2108</v>
+        <v>-1.8938</v>
       </c>
       <c r="P20" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R20" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.778</v>
+        <v>0.0316</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3734</v>
+        <v>0.362</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4046</v>
+        <v>-0.3304</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.2862</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9645</v>
+        <v>-1.6278</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3911</v>
+        <v>-0.1552</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5734</v>
+        <v>-1.4726</v>
       </c>
       <c r="G21" t="n">
         <v>-2.0476</v>
@@ -2092,13 +2092,13 @@
         <v>0.232</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1489</v>
+        <v>0.1878</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2161</v>
+        <v>0.0198</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0672</v>
+        <v>0.168</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4469</v>
+        <v>-2.6435</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9347</v>
+        <v>-1.2885</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5122</v>
+        <v>-1.3549</v>
       </c>
       <c r="G22" t="n">
         <v>-2.8779</v>
@@ -2170,13 +2170,13 @@
         <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8022</v>
+        <v>0.6056</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6097</v>
+        <v>0.2559</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1924</v>
+        <v>0.3497</v>
       </c>
       <c r="V22" t="n">
         <v>0.7886</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C. JONES</t>
+          <t>S. BROWN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.2454</v>
+        <v>-3.2886</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.1994</v>
+        <v>-0.8758</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.046</v>
+        <v>-2.4129</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.1006</v>
+        <v>-0.8808</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.8955</v>
+        <v>0.1297</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.205</v>
+        <v>-1.0104</v>
       </c>
       <c r="J23" t="n">
-        <v>-4.3244</v>
+        <v>0.556</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.7015</v>
+        <v>0.091</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.6229</v>
+        <v>0.465</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7761</v>
+        <v>-1.4368</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1941</v>
+        <v>0.0387</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5821</v>
+        <v>-1.4755</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4639</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.6237</v>
+        <v>-2.7834</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2469</v>
+        <v>0.5199</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6765</v>
+        <v>0.2794</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4296</v>
+        <v>0.2405</v>
       </c>
       <c r="V23" t="n">
-        <v>1.0722</v>
+        <v>-1.0722</v>
       </c>
       <c r="W23" t="n">
         <v>1.0722</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S. BROWN</t>
+          <t>C. JONES</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.2887</v>
+        <v>-3.8357</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.8194</v>
+        <v>-4.0814</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.4693</v>
+        <v>0.2457</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.8808</v>
+        <v>-5.1006</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1297</v>
+        <v>-2.8955</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.0104</v>
+        <v>-2.205</v>
       </c>
       <c r="J24" t="n">
-        <v>0.556</v>
+        <v>-4.3244</v>
       </c>
       <c r="K24" t="n">
-        <v>0.091</v>
+        <v>-2.7015</v>
       </c>
       <c r="L24" t="n">
-        <v>0.465</v>
+        <v>-1.6229</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.4368</v>
+        <v>-0.7761</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0387</v>
+        <v>-0.1941</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.4755</v>
+        <v>-0.5821</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.8556</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.7834</v>
+        <v>-1.6237</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4802</v>
+        <v>0.6565</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6642</v>
+        <v>0.7945</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1841</v>
+        <v>-0.1379</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.0722</v>
+        <v>1.0722</v>
       </c>
       <c r="W24" t="n">
         <v>1.0722</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.5535</v>
+        <v>-5.2669</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.1585</v>
+        <v>-3.8046</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.395</v>
+        <v>-1.4622</v>
       </c>
       <c r="G25" t="n">
         <v>-5.8311</v>
@@ -2404,13 +2404,13 @@
         <v>0.6959</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4182</v>
+        <v>-0.1316</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5895</v>
+        <v>-0.2357</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1713</v>
+        <v>0.1041</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-14.9628</v>
+        <v>-14.1764</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.635800000000001</v>
+        <v>-2.6357</v>
       </c>
       <c r="F26" t="n">
-        <v>-12.327</v>
+        <v>-11.5407</v>
       </c>
       <c r="G26" t="n">
         <v>-13.8676</v>
@@ -2455,7 +2455,7 @@
         <v>-8.933499999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>1.3243</v>
+        <v>1.324300000000001</v>
       </c>
       <c r="K26" t="n">
         <v>-2.9076</v>
@@ -2482,13 +2482,13 @@
         <v>9.2783</v>
       </c>
       <c r="S26" t="n">
-        <v>2.8116</v>
+        <v>3.597799999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>3.5802</v>
+        <v>3.5804</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.7687999999999998</v>
+        <v>0.01749999999999996</v>
       </c>
       <c r="V26" t="n">
         <v>1.8919</v>
